--- a/Investment_Strategy_Example/Config/data_curator_parameters.xlsx
+++ b/Investment_Strategy_Example/Config/data_curator_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KN Hack\Research-Challenge-2026\Investment_Strategy_Example\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7925660C-754C-4D2C-BE63-B4C56390B0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC2C053D-EADB-4958-91FD-FF97F9B6131D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="900" yWindow="3030" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -3809,9 +3809,6 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>851</v>
-      </c>
-      <c r="B2" s="4" t="s">
         <v>661</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -3824,7 +3821,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>912</v>
+        <v>851</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>912</v>
@@ -3836,7 +3833,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>265</v>
+        <v>912</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>265</v>
@@ -3848,7 +3845,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>844</v>
+        <v>265</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>844</v>
@@ -3860,7 +3857,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>266</v>
+        <v>844</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>266</v>
@@ -3872,7 +3869,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>267</v>
@@ -3884,7 +3881,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>268</v>
@@ -3896,7 +3893,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>269</v>
@@ -3908,7 +3905,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>270</v>
@@ -3920,7 +3917,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>834</v>
+        <v>270</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>834</v>
@@ -3932,7 +3929,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>721</v>
+        <v>834</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>721</v>
@@ -3944,7 +3941,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>853</v>
+        <v>721</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>853</v>
@@ -3956,7 +3953,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>271</v>
+        <v>853</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>271</v>
@@ -3968,7 +3965,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>272</v>
@@ -3980,7 +3977,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>273</v>
@@ -3992,7 +3989,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>788</v>
+        <v>273</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>788</v>
@@ -4004,7 +4001,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>757</v>
+        <v>788</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>757</v>
@@ -4016,7 +4013,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>274</v>
+        <v>757</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>274</v>
@@ -4028,7 +4025,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>275</v>
@@ -4040,7 +4037,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>891</v>
+        <v>275</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>891</v>
@@ -4052,7 +4049,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>849</v>
+        <v>891</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>849</v>
@@ -4064,7 +4061,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>767</v>
+        <v>849</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>767</v>
@@ -4076,7 +4073,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>875</v>
+        <v>767</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>875</v>
@@ -4088,7 +4085,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>807</v>
+        <v>875</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>807</v>
@@ -4100,7 +4097,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>796</v>
+        <v>807</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>796</v>
@@ -4112,7 +4109,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>904</v>
+        <v>796</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>904</v>
@@ -4124,7 +4121,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>276</v>
+        <v>904</v>
       </c>
       <c r="C28" s="29" t="s">
         <v>662</v>
@@ -4136,7 +4133,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>276</v>
@@ -4148,7 +4145,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>679</v>
+        <v>277</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>277</v>
@@ -4160,7 +4157,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>278</v>
+        <v>679</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>679</v>
@@ -4172,7 +4169,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>278</v>
@@ -4184,7 +4181,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>279</v>
@@ -4196,7 +4193,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>880</v>
+        <v>280</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>280</v>
@@ -4208,7 +4205,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>281</v>
+        <v>880</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>880</v>
@@ -4220,7 +4217,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>281</v>
@@ -4232,7 +4229,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>282</v>
@@ -4244,7 +4241,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>674</v>
+        <v>283</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>283</v>
@@ -4256,7 +4253,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>284</v>
+        <v>674</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>674</v>
@@ -4268,7 +4265,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>814</v>
+        <v>284</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>284</v>
@@ -4280,7 +4277,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>804</v>
+        <v>814</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>814</v>
@@ -4292,7 +4289,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>285</v>
+        <v>804</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>804</v>
@@ -4304,7 +4301,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>285</v>
@@ -4316,7 +4313,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>286</v>
@@ -4328,7 +4325,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>287</v>
@@ -4340,7 +4337,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>288</v>
@@ -4352,7 +4349,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>866</v>
+        <v>289</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>289</v>
@@ -4364,7 +4361,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>896</v>
+        <v>866</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>866</v>
@@ -4376,7 +4373,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>913</v>
+        <v>896</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>896</v>
@@ -4388,7 +4385,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>749</v>
+        <v>913</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>913</v>
@@ -4400,7 +4397,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>883</v>
+        <v>749</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>749</v>
@@ -4412,7 +4409,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>290</v>
+        <v>883</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>883</v>
@@ -4424,7 +4421,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>833</v>
+        <v>290</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>290</v>
@@ -4436,7 +4433,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>291</v>
+        <v>833</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>833</v>
@@ -4448,7 +4445,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>291</v>
@@ -4460,7 +4457,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>292</v>
@@ -4472,7 +4469,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>878</v>
+        <v>293</v>
       </c>
       <c r="C57" s="29" t="s">
         <v>914</v>
@@ -4484,7 +4481,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>294</v>
+        <v>878</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>293</v>
@@ -4496,7 +4493,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>772</v>
+        <v>294</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>878</v>
@@ -4508,7 +4505,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>718</v>
+        <v>772</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>294</v>
@@ -4520,7 +4517,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>753</v>
+        <v>718</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>772</v>
@@ -4532,7 +4529,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>295</v>
+        <v>753</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>718</v>
@@ -4544,7 +4541,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>832</v>
+        <v>295</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>753</v>
@@ -4556,7 +4553,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>296</v>
+        <v>832</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>295</v>
@@ -4568,7 +4565,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>832</v>
@@ -4580,7 +4577,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>296</v>
@@ -4592,7 +4589,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>297</v>
@@ -4604,7 +4601,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>262</v>
+        <v>299</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>298</v>
@@ -4616,7 +4613,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>854</v>
+        <v>262</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>299</v>
@@ -4628,7 +4625,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>262</v>
@@ -4640,7 +4637,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>300</v>
+        <v>846</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>854</v>
@@ -4652,7 +4649,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>846</v>
@@ -4664,7 +4661,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>300</v>
@@ -4676,7 +4673,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>910</v>
+        <v>302</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>301</v>
@@ -4688,7 +4685,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
-        <v>303</v>
+        <v>910</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>302</v>
@@ -4700,7 +4697,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C76" s="29" t="s">
         <v>915</v>
@@ -4712,7 +4709,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>910</v>
@@ -4724,7 +4721,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>303</v>
@@ -4736,7 +4733,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>916</v>
+        <v>306</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>304</v>
@@ -4748,7 +4745,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>307</v>
+        <v>916</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>305</v>
@@ -4760,7 +4757,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>306</v>
@@ -4772,7 +4769,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>916</v>
@@ -4784,7 +4781,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>734</v>
+        <v>309</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>307</v>
@@ -4796,7 +4793,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
-        <v>310</v>
+        <v>734</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>308</v>
@@ -4808,7 +4805,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C85" s="29" t="s">
         <v>917</v>
@@ -4820,7 +4817,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>309</v>
@@ -4832,7 +4829,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
-        <v>918</v>
+        <v>312</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>734</v>
@@ -4844,7 +4841,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
-        <v>313</v>
+        <v>918</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>310</v>
@@ -4856,7 +4853,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>311</v>
@@ -4868,7 +4865,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
-        <v>812</v>
+        <v>314</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>312</v>
@@ -4880,7 +4877,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
-        <v>315</v>
+        <v>812</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>918</v>
@@ -4892,7 +4889,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>313</v>
@@ -4904,7 +4901,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>314</v>
@@ -4916,7 +4913,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>812</v>
@@ -4928,7 +4925,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
-        <v>242</v>
+        <v>318</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>315</v>
@@ -4940,7 +4937,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
-        <v>319</v>
+        <v>242</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>316</v>
@@ -4952,7 +4949,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>317</v>
@@ -4964,7 +4961,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>318</v>
@@ -4976,7 +4973,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>242</v>
@@ -4988,7 +4985,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>319</v>
@@ -5000,7 +4997,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>320</v>
@@ -5012,7 +5009,7 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>321</v>
@@ -5024,7 +5021,7 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>322</v>
@@ -5036,7 +5033,7 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>323</v>
@@ -5048,7 +5045,7 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
-        <v>856</v>
+        <v>327</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>324</v>
@@ -5060,7 +5057,7 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
-        <v>920</v>
+        <v>856</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>325</v>
@@ -5072,7 +5069,7 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
-        <v>328</v>
+        <v>920</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>326</v>
@@ -5084,7 +5081,7 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
-        <v>801</v>
+        <v>328</v>
       </c>
       <c r="C108" s="29" t="s">
         <v>919</v>
@@ -5096,7 +5093,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
-        <v>329</v>
+        <v>801</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>327</v>
@@ -5108,7 +5105,7 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
-        <v>733</v>
+        <v>329</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>856</v>
@@ -5120,7 +5117,7 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>920</v>
@@ -5132,7 +5129,7 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
-        <v>330</v>
+        <v>744</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>328</v>
@@ -5144,7 +5141,7 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
-        <v>687</v>
+        <v>330</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>801</v>
@@ -5156,7 +5153,7 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
-        <v>667</v>
+        <v>687</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>329</v>
@@ -5168,7 +5165,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
-        <v>921</v>
+        <v>667</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>733</v>
@@ -5180,7 +5177,7 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>744</v>
@@ -5192,7 +5189,7 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>330</v>
@@ -5204,7 +5201,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
-        <v>331</v>
+        <v>923</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>687</v>
@@ -5216,7 +5213,7 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>667</v>
@@ -5228,7 +5225,7 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
-        <v>243</v>
+        <v>332</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>921</v>
@@ -5240,7 +5237,7 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
-        <v>805</v>
+        <v>243</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>922</v>
@@ -5252,7 +5249,7 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
-        <v>333</v>
+        <v>805</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>923</v>
@@ -5264,7 +5261,7 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
-        <v>900</v>
+        <v>333</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>331</v>
@@ -5276,7 +5273,7 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
-        <v>334</v>
+        <v>900</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>332</v>
@@ -5288,7 +5285,7 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>243</v>
@@ -5300,7 +5297,7 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
-        <v>664</v>
+        <v>335</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>805</v>
@@ -5312,7 +5309,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
-        <v>803</v>
+        <v>664</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>333</v>
@@ -5324,7 +5321,7 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
-        <v>336</v>
+        <v>803</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>900</v>
@@ -5336,7 +5333,7 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
-        <v>682</v>
+        <v>336</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>334</v>
@@ -5348,7 +5345,7 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
-        <v>244</v>
+        <v>682</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>335</v>
@@ -5360,7 +5357,7 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
-        <v>888</v>
+        <v>244</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>664</v>
@@ -5372,7 +5369,7 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
-        <v>678</v>
+        <v>888</v>
       </c>
       <c r="C132" s="4" t="s">
         <v>803</v>
@@ -5384,7 +5381,7 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
-        <v>337</v>
+        <v>678</v>
       </c>
       <c r="C133" s="4" t="s">
         <v>336</v>
@@ -5396,7 +5393,7 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C134" s="29" t="s">
         <v>924</v>
@@ -5408,7 +5405,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
-        <v>799</v>
+        <v>338</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>682</v>
@@ -5420,7 +5417,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
-        <v>827</v>
+        <v>799</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>244</v>
@@ -5432,7 +5429,7 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
-        <v>876</v>
+        <v>827</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>888</v>
@@ -5444,7 +5441,7 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
-        <v>339</v>
+        <v>876</v>
       </c>
       <c r="C138" s="4" t="s">
         <v>678</v>
@@ -5456,7 +5453,7 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>337</v>
@@ -5468,7 +5465,7 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>338</v>
@@ -5480,7 +5477,7 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>799</v>
@@ -5492,7 +5489,7 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>827</v>
@@ -5504,7 +5501,7 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>876</v>
@@ -5516,7 +5513,7 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>339</v>
@@ -5528,7 +5525,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C145" s="29" t="s">
         <v>925</v>
@@ -5540,7 +5537,7 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
-        <v>245</v>
+        <v>346</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>340</v>
@@ -5552,7 +5549,7 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
-        <v>669</v>
+        <v>245</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>341</v>
@@ -5564,7 +5561,7 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
-        <v>700</v>
+        <v>669</v>
       </c>
       <c r="C148" s="4" t="s">
         <v>342</v>
@@ -5576,7 +5573,7 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
-        <v>347</v>
+        <v>700</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>343</v>
@@ -5588,7 +5585,7 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
-        <v>817</v>
+        <v>347</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>344</v>
@@ -5600,7 +5597,7 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
-        <v>348</v>
+        <v>817</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>345</v>
@@ -5612,7 +5609,7 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
-        <v>821</v>
+        <v>348</v>
       </c>
       <c r="C152" s="29" t="s">
         <v>926</v>
@@ -5624,7 +5621,7 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
-        <v>911</v>
+        <v>821</v>
       </c>
       <c r="C153" s="4" t="s">
         <v>346</v>
@@ -5636,7 +5633,7 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
-        <v>349</v>
+        <v>911</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>245</v>
@@ -5648,7 +5645,7 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>669</v>
@@ -5660,7 +5657,7 @@
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
-        <v>857</v>
+        <v>350</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>700</v>
@@ -5672,7 +5669,7 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
-        <v>351</v>
+        <v>857</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>347</v>
@@ -5684,7 +5681,7 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>817</v>
@@ -5696,7 +5693,7 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>348</v>
@@ -5708,7 +5705,7 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>821</v>
@@ -5720,7 +5717,7 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
-        <v>852</v>
+        <v>354</v>
       </c>
       <c r="C161" s="29" t="s">
         <v>927</v>
@@ -5732,7 +5729,7 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
-        <v>783</v>
+        <v>852</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>911</v>
@@ -5744,7 +5741,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
-        <v>355</v>
+        <v>783</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>349</v>
@@ -5756,7 +5753,7 @@
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>350</v>
@@ -5768,7 +5765,7 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
-        <v>724</v>
+        <v>356</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>857</v>
@@ -5780,7 +5777,7 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
-        <v>357</v>
+        <v>724</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>351</v>
@@ -5792,7 +5789,7 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
-        <v>928</v>
+        <v>357</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>352</v>
@@ -5804,7 +5801,7 @@
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
-        <v>791</v>
+        <v>928</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>353</v>
@@ -5816,7 +5813,7 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
-        <v>358</v>
+        <v>791</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>354</v>
@@ -5828,7 +5825,7 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
-        <v>873</v>
+        <v>358</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>852</v>
@@ -5840,7 +5837,7 @@
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
-        <v>359</v>
+        <v>873</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>783</v>
@@ -5852,7 +5849,7 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>355</v>
@@ -5864,7 +5861,7 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
-        <v>929</v>
+        <v>360</v>
       </c>
       <c r="C173" s="4" t="s">
         <v>356</v>
@@ -5876,7 +5873,7 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" s="4" t="s">
-        <v>822</v>
+        <v>929</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>724</v>
@@ -5888,7 +5885,7 @@
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
-        <v>841</v>
+        <v>822</v>
       </c>
       <c r="C175" s="4" t="s">
         <v>357</v>
@@ -5900,7 +5897,7 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
-        <v>361</v>
+        <v>841</v>
       </c>
       <c r="C176" s="4" t="s">
         <v>928</v>
@@ -5912,7 +5909,7 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C177" s="4" t="s">
         <v>791</v>
@@ -5924,7 +5921,7 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" s="4" t="s">
-        <v>816</v>
+        <v>362</v>
       </c>
       <c r="C178" s="4" t="s">
         <v>358</v>
@@ -5936,7 +5933,7 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
-        <v>363</v>
+        <v>816</v>
       </c>
       <c r="C179" s="4" t="s">
         <v>873</v>
@@ -5948,7 +5945,7 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>359</v>
@@ -5960,7 +5957,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C181" s="4" t="s">
         <v>360</v>
@@ -5972,7 +5969,7 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C182" s="4" t="s">
         <v>929</v>
@@ -5984,7 +5981,7 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
-        <v>709</v>
+        <v>366</v>
       </c>
       <c r="C183" s="4" t="s">
         <v>822</v>
@@ -5996,7 +5993,7 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" s="4" t="s">
-        <v>367</v>
+        <v>709</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>841</v>
@@ -6008,7 +6005,7 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" s="4" t="s">
-        <v>890</v>
+        <v>367</v>
       </c>
       <c r="C185" s="4" t="s">
         <v>361</v>
@@ -6020,7 +6017,7 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="4" t="s">
-        <v>823</v>
+        <v>890</v>
       </c>
       <c r="C186" s="4" t="s">
         <v>362</v>
@@ -6032,7 +6029,7 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
-        <v>806</v>
+        <v>823</v>
       </c>
       <c r="C187" s="4" t="s">
         <v>816</v>
@@ -6044,7 +6041,7 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" s="4" t="s">
-        <v>368</v>
+        <v>806</v>
       </c>
       <c r="C188" s="4" t="s">
         <v>363</v>
@@ -6056,7 +6053,7 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="4" t="s">
-        <v>781</v>
+        <v>368</v>
       </c>
       <c r="C189" s="4" t="s">
         <v>364</v>
@@ -6068,7 +6065,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" s="4" t="s">
-        <v>369</v>
+        <v>781</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>365</v>
@@ -6080,7 +6077,7 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" s="4" t="s">
-        <v>246</v>
+        <v>369</v>
       </c>
       <c r="C191" s="4" t="s">
         <v>366</v>
@@ -6092,7 +6089,7 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" s="4" t="s">
-        <v>370</v>
+        <v>246</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>709</v>
@@ -6104,7 +6101,7 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C193" s="4" t="s">
         <v>367</v>
@@ -6116,7 +6113,7 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" s="4" t="s">
-        <v>676</v>
+        <v>371</v>
       </c>
       <c r="C194" s="4" t="s">
         <v>890</v>
@@ -6128,7 +6125,7 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" s="4" t="s">
-        <v>694</v>
+        <v>676</v>
       </c>
       <c r="C195" s="4" t="s">
         <v>823</v>
@@ -6140,7 +6137,7 @@
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" s="4" t="s">
-        <v>247</v>
+        <v>694</v>
       </c>
       <c r="C196" s="4" t="s">
         <v>806</v>
@@ -6152,7 +6149,7 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="4" t="s">
-        <v>930</v>
+        <v>247</v>
       </c>
       <c r="C197" s="4" t="s">
         <v>368</v>
@@ -6164,7 +6161,7 @@
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" s="4" t="s">
-        <v>248</v>
+        <v>930</v>
       </c>
       <c r="C198" s="4" t="s">
         <v>781</v>
@@ -6176,7 +6173,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" s="4" t="s">
-        <v>372</v>
+        <v>248</v>
       </c>
       <c r="C199" s="4" t="s">
         <v>369</v>
@@ -6188,7 +6185,7 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>246</v>
@@ -6200,7 +6197,7 @@
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" s="4" t="s">
-        <v>778</v>
+        <v>373</v>
       </c>
       <c r="C201" s="4" t="s">
         <v>370</v>
@@ -6212,7 +6209,7 @@
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" s="4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C202" s="4" t="s">
         <v>371</v>
@@ -6224,7 +6221,7 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" s="4" t="s">
-        <v>893</v>
+        <v>779</v>
       </c>
       <c r="C203" s="4" t="s">
         <v>676</v>
@@ -6236,7 +6233,7 @@
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" s="4" t="s">
-        <v>374</v>
+        <v>893</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>694</v>
@@ -6248,7 +6245,7 @@
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" s="4" t="s">
-        <v>839</v>
+        <v>374</v>
       </c>
       <c r="C205" s="4" t="s">
         <v>247</v>
@@ -6260,7 +6257,7 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" s="4" t="s">
-        <v>731</v>
+        <v>839</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>930</v>
@@ -6272,7 +6269,7 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" s="4" t="s">
-        <v>375</v>
+        <v>731</v>
       </c>
       <c r="C207" s="4" t="s">
         <v>248</v>
@@ -6284,7 +6281,7 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" s="4" t="s">
-        <v>763</v>
+        <v>375</v>
       </c>
       <c r="C208" s="4" t="s">
         <v>372</v>
@@ -6296,7 +6293,7 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" s="4" t="s">
-        <v>376</v>
+        <v>763</v>
       </c>
       <c r="C209" s="4" t="s">
         <v>373</v>
@@ -6308,7 +6305,7 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>778</v>
@@ -6320,7 +6317,7 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" s="4" t="s">
-        <v>695</v>
+        <v>377</v>
       </c>
       <c r="C211" s="4" t="s">
         <v>779</v>
@@ -6332,7 +6329,7 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" s="4" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>893</v>
@@ -6344,7 +6341,7 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" s="4" t="s">
-        <v>795</v>
+        <v>697</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>374</v>
@@ -6356,7 +6353,7 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" s="4" t="s">
-        <v>722</v>
+        <v>795</v>
       </c>
       <c r="C214" s="4" t="s">
         <v>839</v>
@@ -6368,7 +6365,7 @@
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" s="4" t="s">
-        <v>378</v>
+        <v>722</v>
       </c>
       <c r="C215" s="4" t="s">
         <v>731</v>
@@ -6380,7 +6377,7 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>375</v>
@@ -6392,7 +6389,7 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" s="4" t="s">
-        <v>771</v>
+        <v>379</v>
       </c>
       <c r="C217" s="4" t="s">
         <v>763</v>
@@ -6404,7 +6401,7 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" s="4" t="s">
-        <v>380</v>
+        <v>771</v>
       </c>
       <c r="C218" s="4" t="s">
         <v>376</v>
@@ -6416,7 +6413,7 @@
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" s="4" t="s">
-        <v>688</v>
+        <v>380</v>
       </c>
       <c r="C219" s="29" t="s">
         <v>931</v>
@@ -6428,7 +6425,7 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" s="4" t="s">
-        <v>861</v>
+        <v>688</v>
       </c>
       <c r="C220" s="4" t="s">
         <v>377</v>
@@ -6440,7 +6437,7 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" s="4" t="s">
-        <v>932</v>
+        <v>861</v>
       </c>
       <c r="C221" s="4" t="s">
         <v>695</v>
@@ -6452,7 +6449,7 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" s="4" t="s">
-        <v>381</v>
+        <v>932</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>697</v>
@@ -6464,7 +6461,7 @@
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" s="4" t="s">
-        <v>708</v>
+        <v>381</v>
       </c>
       <c r="C223" s="4" t="s">
         <v>795</v>
@@ -6476,7 +6473,7 @@
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" s="4" t="s">
-        <v>382</v>
+        <v>708</v>
       </c>
       <c r="C224" s="4" t="s">
         <v>722</v>
@@ -6488,7 +6485,7 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" s="4" t="s">
-        <v>762</v>
+        <v>382</v>
       </c>
       <c r="C225" s="4" t="s">
         <v>378</v>
@@ -6500,7 +6497,7 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" s="4" t="s">
-        <v>383</v>
+        <v>762</v>
       </c>
       <c r="C226" s="4" t="s">
         <v>379</v>
@@ -6512,7 +6509,7 @@
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" s="4" t="s">
-        <v>703</v>
+        <v>383</v>
       </c>
       <c r="C227" s="4" t="s">
         <v>771</v>
@@ -6524,7 +6521,7 @@
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" s="4" t="s">
-        <v>727</v>
+        <v>703</v>
       </c>
       <c r="C228" s="4" t="s">
         <v>380</v>
@@ -6536,7 +6533,7 @@
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" s="4" t="s">
-        <v>384</v>
+        <v>727</v>
       </c>
       <c r="C229" s="4" t="s">
         <v>688</v>
@@ -6548,7 +6545,7 @@
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" s="4" t="s">
-        <v>745</v>
+        <v>384</v>
       </c>
       <c r="C230" s="4" t="s">
         <v>861</v>
@@ -6560,7 +6557,7 @@
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" s="4" t="s">
-        <v>769</v>
+        <v>745</v>
       </c>
       <c r="C231" s="4" t="s">
         <v>932</v>
@@ -6572,7 +6569,7 @@
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" s="4" t="s">
-        <v>385</v>
+        <v>769</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>381</v>
@@ -6584,7 +6581,7 @@
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C233" s="4" t="s">
         <v>708</v>
@@ -6596,7 +6593,7 @@
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>382</v>
@@ -6608,7 +6605,7 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C235" s="4" t="s">
         <v>762</v>
@@ -6620,7 +6617,7 @@
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" s="4" t="s">
-        <v>907</v>
+        <v>388</v>
       </c>
       <c r="C236" s="4" t="s">
         <v>383</v>
@@ -6632,7 +6629,7 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" s="4" t="s">
-        <v>389</v>
+        <v>907</v>
       </c>
       <c r="C237" s="4" t="s">
         <v>703</v>
@@ -6644,7 +6641,7 @@
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" s="4" t="s">
-        <v>819</v>
+        <v>389</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>727</v>
@@ -6656,7 +6653,7 @@
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" s="4" t="s">
-        <v>390</v>
+        <v>819</v>
       </c>
       <c r="C239" s="4" t="s">
         <v>384</v>
@@ -6668,7 +6665,7 @@
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C240" s="4" t="s">
         <v>745</v>
@@ -6680,7 +6677,7 @@
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" s="4" t="s">
-        <v>670</v>
+        <v>391</v>
       </c>
       <c r="C241" s="4" t="s">
         <v>769</v>
@@ -6692,7 +6689,7 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" s="4" t="s">
-        <v>392</v>
+        <v>670</v>
       </c>
       <c r="C242" s="4" t="s">
         <v>385</v>
@@ -6704,7 +6701,7 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C243" s="4" t="s">
         <v>386</v>
@@ -6716,7 +6713,7 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" s="4" t="s">
-        <v>837</v>
+        <v>393</v>
       </c>
       <c r="C244" s="4" t="s">
         <v>387</v>
@@ -6728,7 +6725,7 @@
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" s="4" t="s">
-        <v>394</v>
+        <v>837</v>
       </c>
       <c r="C245" s="29" t="s">
         <v>933</v>
@@ -6740,7 +6737,7 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C246" s="4" t="s">
         <v>388</v>
@@ -6752,7 +6749,7 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C247" s="4" t="s">
         <v>907</v>
@@ -6764,7 +6761,7 @@
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" s="4" t="s">
-        <v>751</v>
+        <v>396</v>
       </c>
       <c r="C248" s="4" t="s">
         <v>389</v>
@@ -6776,7 +6773,7 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" s="4" t="s">
-        <v>934</v>
+        <v>751</v>
       </c>
       <c r="C249" s="4" t="s">
         <v>819</v>
@@ -6788,7 +6785,7 @@
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" s="4" t="s">
-        <v>249</v>
+        <v>934</v>
       </c>
       <c r="C250" s="4" t="s">
         <v>390</v>
@@ -6800,7 +6797,7 @@
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" s="4" t="s">
-        <v>935</v>
+        <v>249</v>
       </c>
       <c r="C251" s="4" t="s">
         <v>391</v>
@@ -6812,7 +6809,7 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" s="4" t="s">
-        <v>774</v>
+        <v>935</v>
       </c>
       <c r="C252" s="4" t="s">
         <v>670</v>
@@ -6824,7 +6821,7 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" s="4" t="s">
-        <v>855</v>
+        <v>774</v>
       </c>
       <c r="C253" s="4" t="s">
         <v>392</v>
@@ -6836,7 +6833,7 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
-        <v>758</v>
+        <v>855</v>
       </c>
       <c r="C254" s="4" t="s">
         <v>393</v>
@@ -6848,7 +6845,7 @@
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
-        <v>397</v>
+        <v>758</v>
       </c>
       <c r="C255" s="4" t="s">
         <v>837</v>
@@ -6860,7 +6857,7 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" s="4" t="s">
-        <v>737</v>
+        <v>397</v>
       </c>
       <c r="C256" s="4" t="s">
         <v>394</v>
@@ -6872,7 +6869,7 @@
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257" s="4" t="s">
-        <v>250</v>
+        <v>737</v>
       </c>
       <c r="C257" s="4" t="s">
         <v>395</v>
@@ -6884,7 +6881,7 @@
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" s="4" t="s">
-        <v>398</v>
+        <v>250</v>
       </c>
       <c r="C258" s="4" t="s">
         <v>396</v>
@@ -6896,7 +6893,7 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C259" s="4" t="s">
         <v>751</v>
@@ -6908,7 +6905,7 @@
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260" s="4" t="s">
-        <v>701</v>
+        <v>399</v>
       </c>
       <c r="C260" s="4" t="s">
         <v>934</v>
@@ -6920,7 +6917,7 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A261" s="4" t="s">
-        <v>683</v>
+        <v>701</v>
       </c>
       <c r="C261" s="4" t="s">
         <v>249</v>
@@ -6932,7 +6929,7 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A262" s="4" t="s">
-        <v>400</v>
+        <v>683</v>
       </c>
       <c r="C262" s="4" t="s">
         <v>935</v>
@@ -6944,7 +6941,7 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" s="4" t="s">
-        <v>840</v>
+        <v>400</v>
       </c>
       <c r="C263" s="4" t="s">
         <v>774</v>
@@ -6956,7 +6953,7 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A264" s="4" t="s">
-        <v>401</v>
+        <v>840</v>
       </c>
       <c r="C264" s="29" t="s">
         <v>936</v>
@@ -6968,7 +6965,7 @@
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A265" s="4" t="s">
-        <v>712</v>
+        <v>401</v>
       </c>
       <c r="C265" s="4" t="s">
         <v>855</v>
@@ -6980,7 +6977,7 @@
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A266" s="4" t="s">
-        <v>251</v>
+        <v>712</v>
       </c>
       <c r="C266" s="4" t="s">
         <v>758</v>
@@ -6992,7 +6989,7 @@
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A267" s="4" t="s">
-        <v>402</v>
+        <v>251</v>
       </c>
       <c r="C267" s="4" t="s">
         <v>397</v>
@@ -7004,7 +7001,7 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A268" s="4" t="s">
-        <v>786</v>
+        <v>402</v>
       </c>
       <c r="C268" s="4" t="s">
         <v>737</v>
@@ -7016,7 +7013,7 @@
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A269" s="4" t="s">
-        <v>858</v>
+        <v>786</v>
       </c>
       <c r="C269" s="4" t="s">
         <v>250</v>
@@ -7028,7 +7025,7 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A270" s="4" t="s">
-        <v>403</v>
+        <v>858</v>
       </c>
       <c r="C270" s="4" t="s">
         <v>398</v>
@@ -7040,7 +7037,7 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A271" s="4" t="s">
-        <v>908</v>
+        <v>403</v>
       </c>
       <c r="C271" s="4" t="s">
         <v>399</v>
@@ -7052,7 +7049,7 @@
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A272" s="4" t="s">
-        <v>404</v>
+        <v>908</v>
       </c>
       <c r="C272" s="4" t="s">
         <v>701</v>
@@ -7064,7 +7061,7 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A273" s="4" t="s">
-        <v>684</v>
+        <v>404</v>
       </c>
       <c r="C273" s="4" t="s">
         <v>683</v>
@@ -7076,7 +7073,7 @@
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A274" s="4" t="s">
-        <v>405</v>
+        <v>684</v>
       </c>
       <c r="C274" s="4" t="s">
         <v>400</v>
@@ -7088,7 +7085,7 @@
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A275" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C275" s="4" t="s">
         <v>840</v>
@@ -7100,7 +7097,7 @@
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A276" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C276" s="4" t="s">
         <v>401</v>
@@ -7112,7 +7109,7 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A277" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C277" s="4" t="s">
         <v>712</v>
@@ -7124,7 +7121,7 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A278" s="4" t="s">
-        <v>780</v>
+        <v>408</v>
       </c>
       <c r="C278" s="4" t="s">
         <v>251</v>
@@ -7136,7 +7133,7 @@
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A279" s="4" t="s">
-        <v>409</v>
+        <v>780</v>
       </c>
       <c r="C279" s="4" t="s">
         <v>402</v>
@@ -7148,7 +7145,7 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A280" s="4" t="s">
-        <v>879</v>
+        <v>409</v>
       </c>
       <c r="C280" s="4" t="s">
         <v>786</v>
@@ -7160,7 +7157,7 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A281" s="4" t="s">
-        <v>410</v>
+        <v>879</v>
       </c>
       <c r="C281" s="4" t="s">
         <v>858</v>
@@ -7172,7 +7169,7 @@
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A282" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C282" s="4" t="s">
         <v>403</v>
@@ -7184,7 +7181,7 @@
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A283" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C283" s="4" t="s">
         <v>908</v>
@@ -7196,7 +7193,7 @@
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A284" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C284" s="4" t="s">
         <v>404</v>
@@ -7208,7 +7205,7 @@
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A285" s="4" t="s">
-        <v>865</v>
+        <v>413</v>
       </c>
       <c r="C285" s="4" t="s">
         <v>684</v>
@@ -7220,7 +7217,7 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A286" s="4" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
       <c r="C286" s="4" t="s">
         <v>405</v>
@@ -7232,7 +7229,7 @@
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A287" s="4" t="s">
-        <v>792</v>
+        <v>874</v>
       </c>
       <c r="C287" s="4" t="s">
         <v>406</v>
@@ -7244,7 +7241,7 @@
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A288" s="4" t="s">
-        <v>824</v>
+        <v>792</v>
       </c>
       <c r="C288" s="4" t="s">
         <v>407</v>
@@ -7256,7 +7253,7 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A289" s="4" t="s">
-        <v>414</v>
+        <v>824</v>
       </c>
       <c r="C289" s="4" t="s">
         <v>408</v>
@@ -7268,7 +7265,7 @@
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A290" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C290" s="29" t="s">
         <v>937</v>
@@ -7280,7 +7277,7 @@
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A291" s="4" t="s">
-        <v>848</v>
+        <v>415</v>
       </c>
       <c r="C291" s="4" t="s">
         <v>780</v>
@@ -7292,7 +7289,7 @@
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A292" s="4" t="s">
-        <v>789</v>
+        <v>848</v>
       </c>
       <c r="C292" s="4" t="s">
         <v>409</v>
@@ -7304,7 +7301,7 @@
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A293" s="4" t="s">
-        <v>416</v>
+        <v>789</v>
       </c>
       <c r="C293" s="4" t="s">
         <v>879</v>
@@ -7316,7 +7313,7 @@
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A294" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C294" s="4" t="s">
         <v>410</v>
@@ -7328,7 +7325,7 @@
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A295" s="4" t="s">
-        <v>723</v>
+        <v>417</v>
       </c>
       <c r="C295" s="4" t="s">
         <v>411</v>
@@ -7340,7 +7337,7 @@
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A296" s="4" t="s">
-        <v>867</v>
+        <v>723</v>
       </c>
       <c r="C296" s="4" t="s">
         <v>412</v>
@@ -7352,7 +7349,7 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A297" s="4" t="s">
-        <v>418</v>
+        <v>867</v>
       </c>
       <c r="C297" s="29" t="s">
         <v>938</v>
@@ -7364,7 +7361,7 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A298" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C298" s="4" t="s">
         <v>413</v>
@@ -7376,7 +7373,7 @@
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A299" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C299" s="4" t="s">
         <v>865</v>
@@ -7388,7 +7385,7 @@
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A300" s="4" t="s">
-        <v>673</v>
+        <v>420</v>
       </c>
       <c r="C300" s="4" t="s">
         <v>874</v>
@@ -7400,7 +7397,7 @@
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A301" s="4" t="s">
-        <v>421</v>
+        <v>673</v>
       </c>
       <c r="C301" s="4" t="s">
         <v>792</v>
@@ -7412,7 +7409,7 @@
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A302" s="4" t="s">
-        <v>802</v>
+        <v>421</v>
       </c>
       <c r="C302" s="4" t="s">
         <v>824</v>
@@ -7424,7 +7421,7 @@
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A303" s="4" t="s">
-        <v>826</v>
+        <v>802</v>
       </c>
       <c r="C303" s="4" t="s">
         <v>414</v>
@@ -7436,7 +7433,7 @@
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A304" s="4" t="s">
-        <v>422</v>
+        <v>826</v>
       </c>
       <c r="C304" s="4" t="s">
         <v>415</v>
@@ -7448,7 +7445,7 @@
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A305" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C305" s="4" t="s">
         <v>848</v>
@@ -7460,7 +7457,7 @@
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A306" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C306" s="4" t="s">
         <v>789</v>
@@ -7472,7 +7469,7 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A307" s="4" t="s">
-        <v>252</v>
+        <v>424</v>
       </c>
       <c r="C307" s="4" t="s">
         <v>416</v>
@@ -7484,7 +7481,7 @@
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A308" s="4" t="s">
-        <v>425</v>
+        <v>252</v>
       </c>
       <c r="C308" s="4" t="s">
         <v>417</v>
@@ -7496,7 +7493,7 @@
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A309" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C309" s="4" t="s">
         <v>723</v>
@@ -7508,7 +7505,7 @@
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A310" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C310" s="4" t="s">
         <v>867</v>
@@ -7520,7 +7517,7 @@
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A311" s="4" t="s">
-        <v>906</v>
+        <v>427</v>
       </c>
       <c r="C311" s="4" t="s">
         <v>418</v>
@@ -7532,7 +7529,7 @@
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A312" s="4" t="s">
-        <v>428</v>
+        <v>906</v>
       </c>
       <c r="C312" s="4" t="s">
         <v>419</v>
@@ -7544,7 +7541,7 @@
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A313" s="4" t="s">
-        <v>889</v>
+        <v>428</v>
       </c>
       <c r="C313" s="4" t="s">
         <v>420</v>
@@ -7556,7 +7553,7 @@
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A314" s="4" t="s">
-        <v>429</v>
+        <v>889</v>
       </c>
       <c r="C314" s="4" t="s">
         <v>673</v>
@@ -7568,7 +7565,7 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A315" s="4" t="s">
-        <v>828</v>
+        <v>429</v>
       </c>
       <c r="C315" s="4" t="s">
         <v>421</v>
@@ -7580,7 +7577,7 @@
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A316" s="4" t="s">
-        <v>430</v>
+        <v>828</v>
       </c>
       <c r="C316" s="4" t="s">
         <v>802</v>
@@ -7592,7 +7589,7 @@
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A317" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C317" s="29" t="s">
         <v>939</v>
@@ -7604,7 +7601,7 @@
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A318" s="4" t="s">
-        <v>813</v>
+        <v>431</v>
       </c>
       <c r="C318" s="4" t="s">
         <v>826</v>
@@ -7616,7 +7613,7 @@
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A319" s="4" t="s">
-        <v>432</v>
+        <v>813</v>
       </c>
       <c r="C319" s="4" t="s">
         <v>422</v>
@@ -7628,7 +7625,7 @@
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A320" s="4" t="s">
-        <v>699</v>
+        <v>432</v>
       </c>
       <c r="C320" s="4" t="s">
         <v>423</v>
@@ -7640,7 +7637,7 @@
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A321" s="4" t="s">
-        <v>720</v>
+        <v>699</v>
       </c>
       <c r="C321" s="4" t="s">
         <v>424</v>
@@ -7652,7 +7649,7 @@
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A322" s="4" t="s">
-        <v>433</v>
+        <v>720</v>
       </c>
       <c r="C322" s="29" t="s">
         <v>940</v>
@@ -7664,7 +7661,7 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A323" s="4" t="s">
-        <v>808</v>
+        <v>433</v>
       </c>
       <c r="C323" s="4" t="s">
         <v>252</v>
@@ -7676,7 +7673,7 @@
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A324" s="4" t="s">
-        <v>434</v>
+        <v>808</v>
       </c>
       <c r="C324" s="4" t="s">
         <v>425</v>
@@ -7688,7 +7685,7 @@
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A325" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C325" s="4" t="s">
         <v>426</v>
@@ -7700,7 +7697,7 @@
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A326" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C326" s="4" t="s">
         <v>427</v>
@@ -7712,7 +7709,7 @@
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A327" s="4" t="s">
-        <v>741</v>
+        <v>436</v>
       </c>
       <c r="C327" s="4" t="s">
         <v>906</v>
@@ -7724,7 +7721,7 @@
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A328" s="4" t="s">
-        <v>850</v>
+        <v>741</v>
       </c>
       <c r="C328" s="4" t="s">
         <v>428</v>
@@ -7736,7 +7733,7 @@
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A329" s="4" t="s">
-        <v>759</v>
+        <v>850</v>
       </c>
       <c r="C329" s="4" t="s">
         <v>889</v>
@@ -7748,7 +7745,7 @@
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A330" s="4" t="s">
-        <v>437</v>
+        <v>759</v>
       </c>
       <c r="C330" s="4" t="s">
         <v>429</v>
@@ -7760,7 +7757,7 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A331" s="4" t="s">
-        <v>884</v>
+        <v>437</v>
       </c>
       <c r="C331" s="4" t="s">
         <v>828</v>
@@ -7772,7 +7769,7 @@
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A332" s="4" t="s">
-        <v>732</v>
+        <v>884</v>
       </c>
       <c r="C332" s="4" t="s">
         <v>430</v>
@@ -7784,7 +7781,7 @@
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A333" s="4" t="s">
-        <v>438</v>
+        <v>732</v>
       </c>
       <c r="C333" s="4" t="s">
         <v>431</v>
@@ -7796,7 +7793,7 @@
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A334" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C334" s="4" t="s">
         <v>813</v>
@@ -7808,7 +7805,7 @@
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A335" s="4" t="s">
-        <v>725</v>
+        <v>439</v>
       </c>
       <c r="C335" s="4" t="s">
         <v>432</v>
@@ -7820,7 +7817,7 @@
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A336" s="4" t="s">
-        <v>943</v>
+        <v>725</v>
       </c>
       <c r="C336" s="4" t="s">
         <v>699</v>
@@ -7832,7 +7829,7 @@
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A337" s="4" t="s">
-        <v>787</v>
+        <v>943</v>
       </c>
       <c r="C337" s="4" t="s">
         <v>720</v>
@@ -7844,7 +7841,7 @@
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A338" s="4" t="s">
-        <v>440</v>
+        <v>787</v>
       </c>
       <c r="C338" s="4" t="s">
         <v>433</v>
@@ -7856,7 +7853,7 @@
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A339" s="4" t="s">
-        <v>766</v>
+        <v>440</v>
       </c>
       <c r="C339" s="29" t="s">
         <v>941</v>
@@ -7868,7 +7865,7 @@
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A340" s="4" t="s">
-        <v>666</v>
+        <v>766</v>
       </c>
       <c r="C340" s="4" t="s">
         <v>808</v>
@@ -7880,7 +7877,7 @@
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A341" s="4" t="s">
-        <v>441</v>
+        <v>666</v>
       </c>
       <c r="C341" s="29" t="s">
         <v>942</v>
@@ -7892,7 +7889,7 @@
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A342" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C342" s="4" t="s">
         <v>434</v>
@@ -7904,7 +7901,7 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A343" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C343" s="4" t="s">
         <v>435</v>
@@ -7916,7 +7913,7 @@
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A344" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C344" s="4" t="s">
         <v>436</v>
@@ -7928,7 +7925,7 @@
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A345" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C345" s="4" t="s">
         <v>741</v>
@@ -7940,7 +7937,7 @@
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A346" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C346" s="4" t="s">
         <v>850</v>
@@ -7952,7 +7949,7 @@
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A347" s="4" t="s">
-        <v>905</v>
+        <v>446</v>
       </c>
       <c r="C347" s="4" t="s">
         <v>759</v>
@@ -7964,7 +7961,7 @@
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A348" s="4" t="s">
-        <v>447</v>
+        <v>905</v>
       </c>
       <c r="C348" s="4" t="s">
         <v>437</v>
@@ -7976,7 +7973,7 @@
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A349" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C349" s="4" t="s">
         <v>884</v>
@@ -7988,7 +7985,7 @@
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A350" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C350" s="4" t="s">
         <v>732</v>
@@ -8000,7 +7997,7 @@
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A351" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C351" s="4" t="s">
         <v>438</v>
@@ -8012,7 +8009,7 @@
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A352" s="4" t="s">
-        <v>864</v>
+        <v>450</v>
       </c>
       <c r="C352" s="4" t="s">
         <v>439</v>
@@ -8024,7 +8021,7 @@
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A353" s="4" t="s">
-        <v>784</v>
+        <v>864</v>
       </c>
       <c r="C353" s="4" t="s">
         <v>725</v>
@@ -8036,7 +8033,7 @@
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A354" s="4" t="s">
-        <v>944</v>
+        <v>784</v>
       </c>
       <c r="C354" s="4" t="s">
         <v>943</v>
@@ -8048,7 +8045,7 @@
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A355" s="4" t="s">
-        <v>451</v>
+        <v>944</v>
       </c>
       <c r="C355" s="4" t="s">
         <v>787</v>
@@ -8060,7 +8057,7 @@
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A356" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C356" s="4" t="s">
         <v>440</v>
@@ -8072,7 +8069,7 @@
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A357" s="4" t="s">
-        <v>746</v>
+        <v>452</v>
       </c>
       <c r="C357" s="4" t="s">
         <v>766</v>
@@ -8084,7 +8081,7 @@
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A358" s="4" t="s">
-        <v>785</v>
+        <v>746</v>
       </c>
       <c r="C358" s="4" t="s">
         <v>666</v>
@@ -8096,7 +8093,7 @@
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A359" s="4" t="s">
-        <v>453</v>
+        <v>785</v>
       </c>
       <c r="C359" s="4" t="s">
         <v>441</v>
@@ -8108,7 +8105,7 @@
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A360" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C360" s="4" t="s">
         <v>442</v>
@@ -8120,7 +8117,7 @@
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A361" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C361" s="4" t="s">
         <v>443</v>
@@ -8132,7 +8129,7 @@
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A362" s="4" t="s">
-        <v>860</v>
+        <v>455</v>
       </c>
       <c r="C362" s="4" t="s">
         <v>444</v>
@@ -8144,7 +8141,7 @@
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A363" s="4" t="s">
-        <v>456</v>
+        <v>860</v>
       </c>
       <c r="C363" s="4" t="s">
         <v>445</v>
@@ -8156,7 +8153,7 @@
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A364" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C364" s="4" t="s">
         <v>446</v>
@@ -8168,7 +8165,7 @@
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A365" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C365" s="4" t="s">
         <v>905</v>
@@ -8180,7 +8177,7 @@
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A366" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C366" s="4" t="s">
         <v>447</v>
@@ -8192,7 +8189,7 @@
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A367" s="4" t="s">
-        <v>811</v>
+        <v>459</v>
       </c>
       <c r="C367" s="4" t="s">
         <v>448</v>
@@ -8204,7 +8201,7 @@
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A368" s="4" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="C368" s="4" t="s">
         <v>449</v>
@@ -8216,7 +8213,7 @@
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A369" s="4" t="s">
-        <v>881</v>
+        <v>818</v>
       </c>
       <c r="C369" s="4" t="s">
         <v>450</v>
@@ -8228,7 +8225,7 @@
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A370" s="4" t="s">
-        <v>460</v>
+        <v>881</v>
       </c>
       <c r="C370" s="4" t="s">
         <v>864</v>
@@ -8240,7 +8237,7 @@
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A371" s="4" t="s">
-        <v>702</v>
+        <v>460</v>
       </c>
       <c r="C371" s="4" t="s">
         <v>784</v>
@@ -8252,7 +8249,7 @@
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A372" s="4" t="s">
-        <v>726</v>
+        <v>702</v>
       </c>
       <c r="C372" s="4" t="s">
         <v>944</v>
@@ -8264,7 +8261,7 @@
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A373" s="4" t="s">
-        <v>461</v>
+        <v>726</v>
       </c>
       <c r="C373" s="4" t="s">
         <v>451</v>
@@ -8276,7 +8273,7 @@
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A374" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C374" s="4" t="s">
         <v>452</v>
@@ -8288,7 +8285,7 @@
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A375" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C375" s="4" t="s">
         <v>746</v>
@@ -8300,7 +8297,7 @@
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A376" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C376" s="4" t="s">
         <v>785</v>
@@ -8312,7 +8309,7 @@
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A377" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C377" s="4" t="s">
         <v>453</v>
@@ -8324,7 +8321,7 @@
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A378" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C378" s="4" t="s">
         <v>454</v>
@@ -8336,7 +8333,7 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A379" s="4" t="s">
-        <v>253</v>
+        <v>466</v>
       </c>
       <c r="C379" s="4" t="s">
         <v>455</v>
@@ -8348,7 +8345,7 @@
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A380" s="4" t="s">
-        <v>738</v>
+        <v>253</v>
       </c>
       <c r="C380" s="4" t="s">
         <v>860</v>
@@ -8360,7 +8357,7 @@
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A381" s="4" t="s">
-        <v>845</v>
+        <v>738</v>
       </c>
       <c r="C381" s="4" t="s">
         <v>456</v>
@@ -8372,7 +8369,7 @@
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A382" s="4" t="s">
-        <v>467</v>
+        <v>845</v>
       </c>
       <c r="C382" s="4" t="s">
         <v>457</v>
@@ -8384,7 +8381,7 @@
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A383" s="4" t="s">
-        <v>903</v>
+        <v>467</v>
       </c>
       <c r="C383" s="4" t="s">
         <v>458</v>
@@ -8396,7 +8393,7 @@
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A384" s="4" t="s">
-        <v>713</v>
+        <v>903</v>
       </c>
       <c r="C384" s="4" t="s">
         <v>459</v>
@@ -8408,7 +8405,7 @@
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A385" s="4" t="s">
-        <v>468</v>
+        <v>713</v>
       </c>
       <c r="C385" s="4" t="s">
         <v>811</v>
@@ -8420,7 +8417,7 @@
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A386" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C386" s="4" t="s">
         <v>818</v>
@@ -8432,7 +8429,7 @@
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A387" s="4" t="s">
-        <v>820</v>
+        <v>469</v>
       </c>
       <c r="C387" s="4" t="s">
         <v>881</v>
@@ -8444,7 +8441,7 @@
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A388" s="4" t="s">
-        <v>947</v>
+        <v>820</v>
       </c>
       <c r="C388" s="4" t="s">
         <v>460</v>
@@ -8456,7 +8453,7 @@
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A389" s="4" t="s">
-        <v>470</v>
+        <v>947</v>
       </c>
       <c r="C389" s="4" t="s">
         <v>702</v>
@@ -8468,7 +8465,7 @@
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A390" s="4" t="s">
-        <v>897</v>
+        <v>470</v>
       </c>
       <c r="C390" s="4" t="s">
         <v>726</v>
@@ -8480,7 +8477,7 @@
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A391" s="4" t="s">
-        <v>471</v>
+        <v>897</v>
       </c>
       <c r="C391" s="4" t="s">
         <v>461</v>
@@ -8492,7 +8489,7 @@
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A392" s="4" t="s">
-        <v>747</v>
+        <v>471</v>
       </c>
       <c r="C392" s="29" t="s">
         <v>945</v>
@@ -8504,7 +8501,7 @@
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A393" s="4" t="s">
-        <v>809</v>
+        <v>747</v>
       </c>
       <c r="C393" s="4" t="s">
         <v>462</v>
@@ -8516,7 +8513,7 @@
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A394" s="4" t="s">
-        <v>472</v>
+        <v>809</v>
       </c>
       <c r="C394" s="29" t="s">
         <v>946</v>
@@ -8528,7 +8525,7 @@
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A395" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C395" s="4" t="s">
         <v>463</v>
@@ -8540,7 +8537,7 @@
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A396" s="4" t="s">
-        <v>899</v>
+        <v>473</v>
       </c>
       <c r="C396" s="4" t="s">
         <v>464</v>
@@ -8552,7 +8549,7 @@
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A397" s="4" t="s">
-        <v>692</v>
+        <v>899</v>
       </c>
       <c r="C397" s="4" t="s">
         <v>465</v>
@@ -8564,7 +8561,7 @@
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A398" s="4" t="s">
-        <v>474</v>
+        <v>692</v>
       </c>
       <c r="C398" s="4" t="s">
         <v>466</v>
@@ -8576,7 +8573,7 @@
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A399" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C399" s="4" t="s">
         <v>253</v>
@@ -8588,7 +8585,7 @@
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A400" s="4" t="s">
-        <v>752</v>
+        <v>475</v>
       </c>
       <c r="C400" s="4" t="s">
         <v>738</v>
@@ -8600,7 +8597,7 @@
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A401" s="4" t="s">
-        <v>707</v>
+        <v>752</v>
       </c>
       <c r="C401" s="4" t="s">
         <v>845</v>
@@ -8612,7 +8609,7 @@
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A402" s="4" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C402" s="4" t="s">
         <v>467</v>
@@ -8624,7 +8621,7 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A403" s="4" t="s">
-        <v>476</v>
+        <v>704</v>
       </c>
       <c r="C403" s="4" t="s">
         <v>903</v>
@@ -8636,7 +8633,7 @@
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A404" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C404" s="4" t="s">
         <v>713</v>
@@ -8648,7 +8645,7 @@
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A405" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C405" s="4" t="s">
         <v>468</v>
@@ -8660,7 +8657,7 @@
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A406" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C406" s="4" t="s">
         <v>469</v>
@@ -8672,7 +8669,7 @@
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A407" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C407" s="4" t="s">
         <v>820</v>
@@ -8684,7 +8681,7 @@
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A408" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C408" s="4" t="s">
         <v>947</v>
@@ -8696,7 +8693,7 @@
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A409" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C409" s="4" t="s">
         <v>470</v>
@@ -8708,7 +8705,7 @@
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A410" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C410" s="4" t="s">
         <v>897</v>
@@ -8720,7 +8717,7 @@
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A411" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C411" s="4" t="s">
         <v>471</v>
@@ -8732,7 +8729,7 @@
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A412" s="4" t="s">
-        <v>677</v>
+        <v>484</v>
       </c>
       <c r="C412" s="4" t="s">
         <v>747</v>
@@ -8744,7 +8741,7 @@
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A413" s="4" t="s">
-        <v>887</v>
+        <v>677</v>
       </c>
       <c r="C413" s="4" t="s">
         <v>809</v>
@@ -8756,7 +8753,7 @@
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A414" s="4" t="s">
-        <v>485</v>
+        <v>887</v>
       </c>
       <c r="C414" s="4" t="s">
         <v>472</v>
@@ -8768,7 +8765,7 @@
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A415" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C415" s="29" t="s">
         <v>948</v>
@@ -8780,7 +8777,7 @@
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A416" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C416" s="4" t="s">
         <v>473</v>
@@ -8792,7 +8789,7 @@
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A417" s="4" t="s">
-        <v>736</v>
+        <v>487</v>
       </c>
       <c r="C417" s="4" t="s">
         <v>899</v>
@@ -8804,7 +8801,7 @@
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A418" s="4" t="s">
-        <v>892</v>
+        <v>736</v>
       </c>
       <c r="C418" s="4" t="s">
         <v>692</v>
@@ -8816,7 +8813,7 @@
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A419" s="4" t="s">
-        <v>739</v>
+        <v>892</v>
       </c>
       <c r="C419" s="4" t="s">
         <v>474</v>
@@ -8828,7 +8825,7 @@
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A420" s="4" t="s">
-        <v>488</v>
+        <v>739</v>
       </c>
       <c r="C420" s="4" t="s">
         <v>475</v>
@@ -8840,7 +8837,7 @@
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A421" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C421" s="4" t="s">
         <v>752</v>
@@ -8852,7 +8849,7 @@
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A422" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C422" s="4" t="s">
         <v>707</v>
@@ -8864,7 +8861,7 @@
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A423" s="4" t="s">
-        <v>843</v>
+        <v>490</v>
       </c>
       <c r="C423" s="4" t="s">
         <v>704</v>
@@ -8876,7 +8873,7 @@
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A424" s="4" t="s">
-        <v>491</v>
+        <v>843</v>
       </c>
       <c r="C424" s="4" t="s">
         <v>476</v>
@@ -8888,7 +8885,7 @@
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A425" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C425" s="4" t="s">
         <v>477</v>
@@ -8900,7 +8897,7 @@
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A426" s="4" t="s">
-        <v>254</v>
+        <v>492</v>
       </c>
       <c r="C426" s="4" t="s">
         <v>478</v>
@@ -8912,7 +8909,7 @@
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A427" s="4" t="s">
-        <v>493</v>
+        <v>254</v>
       </c>
       <c r="C427" s="4" t="s">
         <v>479</v>
@@ -8924,7 +8921,7 @@
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A428" s="4" t="s">
-        <v>949</v>
+        <v>493</v>
       </c>
       <c r="C428" s="4" t="s">
         <v>480</v>
@@ -8936,7 +8933,7 @@
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A429" s="4" t="s">
-        <v>494</v>
+        <v>949</v>
       </c>
       <c r="C429" s="4" t="s">
         <v>481</v>
@@ -8948,7 +8945,7 @@
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A430" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C430" s="4" t="s">
         <v>482</v>
@@ -8960,7 +8957,7 @@
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A431" s="4" t="s">
-        <v>719</v>
+        <v>495</v>
       </c>
       <c r="C431" s="4" t="s">
         <v>483</v>
@@ -8972,7 +8969,7 @@
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A432" s="4" t="s">
-        <v>950</v>
+        <v>719</v>
       </c>
       <c r="C432" s="4" t="s">
         <v>484</v>
@@ -8984,7 +8981,7 @@
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A433" s="4" t="s">
-        <v>496</v>
+        <v>950</v>
       </c>
       <c r="C433" s="4" t="s">
         <v>677</v>
@@ -8996,7 +8993,7 @@
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A434" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C434" s="4" t="s">
         <v>887</v>
@@ -9008,7 +9005,7 @@
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A435" s="4" t="s">
-        <v>895</v>
+        <v>497</v>
       </c>
       <c r="C435" s="4" t="s">
         <v>485</v>
@@ -9020,7 +9017,7 @@
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A436" s="4" t="s">
-        <v>870</v>
+        <v>895</v>
       </c>
       <c r="C436" s="4" t="s">
         <v>486</v>
@@ -9032,7 +9029,7 @@
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A437" s="4" t="s">
-        <v>498</v>
+        <v>870</v>
       </c>
       <c r="C437" s="4" t="s">
         <v>487</v>
@@ -9044,7 +9041,7 @@
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A438" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C438" s="4" t="s">
         <v>736</v>
@@ -9056,7 +9053,7 @@
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A439" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C439" s="4" t="s">
         <v>892</v>
@@ -9068,7 +9065,7 @@
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A440" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C440" s="4" t="s">
         <v>739</v>
@@ -9080,7 +9077,7 @@
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A441" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C441" s="4" t="s">
         <v>488</v>
@@ -9092,7 +9089,7 @@
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A442" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C442" s="4" t="s">
         <v>489</v>
@@ -9104,7 +9101,7 @@
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A443" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C443" s="4" t="s">
         <v>490</v>
@@ -9116,7 +9113,7 @@
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A444" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C444" s="4" t="s">
         <v>843</v>
@@ -9128,7 +9125,7 @@
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A445" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C445" s="4" t="s">
         <v>491</v>
@@ -9140,7 +9137,7 @@
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A446" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C446" s="4" t="s">
         <v>492</v>
@@ -9152,7 +9149,7 @@
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A447" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C447" s="4" t="s">
         <v>254</v>
@@ -9164,7 +9161,7 @@
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A448" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C448" s="4" t="s">
         <v>493</v>
@@ -9176,7 +9173,7 @@
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A449" s="4" t="s">
-        <v>952</v>
+        <v>509</v>
       </c>
       <c r="C449" s="4" t="s">
         <v>949</v>
@@ -9188,7 +9185,7 @@
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A450" s="4" t="s">
-        <v>510</v>
+        <v>952</v>
       </c>
       <c r="C450" s="4" t="s">
         <v>494</v>
@@ -9200,7 +9197,7 @@
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A451" s="4" t="s">
-        <v>953</v>
+        <v>510</v>
       </c>
       <c r="C451" s="4" t="s">
         <v>495</v>
@@ -9212,7 +9209,7 @@
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A452" s="4" t="s">
-        <v>263</v>
+        <v>953</v>
       </c>
       <c r="C452" s="4" t="s">
         <v>719</v>
@@ -9224,7 +9221,7 @@
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A453" s="4" t="s">
-        <v>894</v>
+        <v>263</v>
       </c>
       <c r="C453" s="4" t="s">
         <v>950</v>
@@ -9236,7 +9233,7 @@
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A454" s="4" t="s">
-        <v>511</v>
+        <v>894</v>
       </c>
       <c r="C454" s="4" t="s">
         <v>496</v>
@@ -9248,7 +9245,7 @@
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A455" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C455" s="4" t="s">
         <v>497</v>
@@ -9260,7 +9257,7 @@
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A456" s="4" t="s">
-        <v>255</v>
+        <v>512</v>
       </c>
       <c r="C456" s="4" t="s">
         <v>895</v>
@@ -9272,7 +9269,7 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A457" s="4" t="s">
-        <v>513</v>
+        <v>255</v>
       </c>
       <c r="C457" s="4" t="s">
         <v>870</v>
@@ -9284,7 +9281,7 @@
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A458" s="4" t="s">
-        <v>690</v>
+        <v>513</v>
       </c>
       <c r="C458" s="4" t="s">
         <v>498</v>
@@ -9296,7 +9293,7 @@
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A459" s="4" t="s">
-        <v>514</v>
+        <v>690</v>
       </c>
       <c r="C459" s="4" t="s">
         <v>499</v>
@@ -9308,7 +9305,7 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A460" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C460" s="4" t="s">
         <v>500</v>
@@ -9320,7 +9317,7 @@
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A461" s="4" t="s">
-        <v>728</v>
+        <v>515</v>
       </c>
       <c r="C461" s="4" t="s">
         <v>501</v>
@@ -9332,7 +9329,7 @@
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A462" s="4" t="s">
-        <v>516</v>
+        <v>728</v>
       </c>
       <c r="C462" s="4" t="s">
         <v>502</v>
@@ -9344,7 +9341,7 @@
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A463" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C463" s="4" t="s">
         <v>503</v>
@@ -9356,7 +9353,7 @@
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A464" s="4" t="s">
-        <v>256</v>
+        <v>517</v>
       </c>
       <c r="C464" s="4" t="s">
         <v>504</v>
@@ -9368,7 +9365,7 @@
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A465" s="4" t="s">
-        <v>518</v>
+        <v>256</v>
       </c>
       <c r="C465" s="4" t="s">
         <v>505</v>
@@ -9380,7 +9377,7 @@
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A466" s="4" t="s">
-        <v>909</v>
+        <v>518</v>
       </c>
       <c r="C466" s="4" t="s">
         <v>506</v>
@@ -9392,7 +9389,7 @@
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A467" s="4" t="s">
-        <v>773</v>
+        <v>909</v>
       </c>
       <c r="C467" s="4" t="s">
         <v>507</v>
@@ -9404,7 +9401,7 @@
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A468" s="4" t="s">
-        <v>730</v>
+        <v>773</v>
       </c>
       <c r="C468" s="4" t="s">
         <v>508</v>
@@ -9416,7 +9413,7 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A469" s="4" t="s">
-        <v>519</v>
+        <v>730</v>
       </c>
       <c r="C469" s="29" t="s">
         <v>951</v>
@@ -9428,7 +9425,7 @@
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A470" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C470" s="4" t="s">
         <v>509</v>
@@ -9440,7 +9437,7 @@
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A471" s="4" t="s">
-        <v>714</v>
+        <v>520</v>
       </c>
       <c r="C471" s="4" t="s">
         <v>952</v>
@@ -9452,7 +9449,7 @@
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A472" s="4" t="s">
-        <v>521</v>
+        <v>714</v>
       </c>
       <c r="C472" s="4" t="s">
         <v>510</v>
@@ -9464,7 +9461,7 @@
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A473" s="4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C473" s="4" t="s">
         <v>953</v>
@@ -9476,7 +9473,7 @@
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A474" s="4" t="s">
-        <v>825</v>
+        <v>522</v>
       </c>
       <c r="C474" s="4" t="s">
         <v>263</v>
@@ -9488,7 +9485,7 @@
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A475" s="4" t="s">
-        <v>523</v>
+        <v>825</v>
       </c>
       <c r="C475" s="4" t="s">
         <v>894</v>
@@ -9500,7 +9497,7 @@
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A476" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C476" s="4" t="s">
         <v>511</v>
@@ -9512,7 +9509,7 @@
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A477" s="4" t="s">
-        <v>847</v>
+        <v>524</v>
       </c>
       <c r="C477" s="4" t="s">
         <v>512</v>
@@ -9524,7 +9521,7 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A478" s="4" t="s">
-        <v>525</v>
+        <v>847</v>
       </c>
       <c r="C478" s="4" t="s">
         <v>255</v>
@@ -9536,7 +9533,7 @@
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A479" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C479" s="4" t="s">
         <v>513</v>
@@ -9548,7 +9545,7 @@
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A480" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C480" s="4" t="s">
         <v>690</v>
@@ -9560,7 +9557,7 @@
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A481" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C481" s="4" t="s">
         <v>514</v>
@@ -9572,7 +9569,7 @@
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A482" s="4" t="s">
-        <v>810</v>
+        <v>528</v>
       </c>
       <c r="C482" s="4" t="s">
         <v>515</v>
@@ -9584,7 +9581,7 @@
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A483" s="4" t="s">
-        <v>748</v>
+        <v>810</v>
       </c>
       <c r="C483" s="4" t="s">
         <v>728</v>
@@ -9596,7 +9593,7 @@
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A484" s="4" t="s">
-        <v>711</v>
+        <v>748</v>
       </c>
       <c r="C484" s="4" t="s">
         <v>516</v>
@@ -9608,7 +9605,7 @@
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A485" s="4" t="s">
-        <v>529</v>
+        <v>711</v>
       </c>
       <c r="C485" s="4" t="s">
         <v>517</v>
@@ -9620,7 +9617,7 @@
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A486" s="4" t="s">
-        <v>671</v>
+        <v>529</v>
       </c>
       <c r="C486" s="4" t="s">
         <v>256</v>
@@ -9632,7 +9629,7 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A487" s="4" t="s">
-        <v>715</v>
+        <v>671</v>
       </c>
       <c r="C487" s="4" t="s">
         <v>518</v>
@@ -9644,7 +9641,7 @@
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A488" s="4" t="s">
-        <v>530</v>
+        <v>715</v>
       </c>
       <c r="C488" s="4" t="s">
         <v>909</v>
@@ -9656,7 +9653,7 @@
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A489" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C489" s="4" t="s">
         <v>773</v>
@@ -9668,7 +9665,7 @@
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A490" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C490" s="4" t="s">
         <v>730</v>
@@ -9680,7 +9677,7 @@
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A491" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C491" s="4" t="s">
         <v>519</v>
@@ -9692,7 +9689,7 @@
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A492" s="4" t="s">
-        <v>257</v>
+        <v>533</v>
       </c>
       <c r="C492" s="4" t="s">
         <v>520</v>
@@ -9704,7 +9701,7 @@
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A493" s="4" t="s">
-        <v>534</v>
+        <v>257</v>
       </c>
       <c r="C493" s="4" t="s">
         <v>714</v>
@@ -9716,7 +9713,7 @@
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A494" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C494" s="4" t="s">
         <v>521</v>
@@ -9728,7 +9725,7 @@
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A495" s="4" t="s">
-        <v>898</v>
+        <v>535</v>
       </c>
       <c r="C495" s="4" t="s">
         <v>522</v>
@@ -9740,7 +9737,7 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A496" s="4" t="s">
-        <v>536</v>
+        <v>898</v>
       </c>
       <c r="C496" s="4" t="s">
         <v>825</v>
@@ -9752,7 +9749,7 @@
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A497" s="4" t="s">
-        <v>698</v>
+        <v>536</v>
       </c>
       <c r="C497" s="4" t="s">
         <v>523</v>
@@ -9764,7 +9761,7 @@
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A498" s="4" t="s">
-        <v>537</v>
+        <v>698</v>
       </c>
       <c r="C498" s="4" t="s">
         <v>524</v>
@@ -9776,7 +9773,7 @@
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A499" s="4" t="s">
-        <v>955</v>
+        <v>537</v>
       </c>
       <c r="C499" s="4" t="s">
         <v>847</v>
@@ -9788,7 +9785,7 @@
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A500" s="4" t="s">
-        <v>863</v>
+        <v>955</v>
       </c>
       <c r="C500" s="4" t="s">
         <v>525</v>
@@ -9800,7 +9797,7 @@
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A501" s="4" t="s">
-        <v>258</v>
+        <v>863</v>
       </c>
       <c r="C501" s="4" t="s">
         <v>526</v>
@@ -9812,7 +9809,7 @@
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A502" s="4" t="s">
-        <v>665</v>
+        <v>258</v>
       </c>
       <c r="C502" s="4" t="s">
         <v>527</v>
@@ -9824,7 +9821,7 @@
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A503" s="4" t="s">
-        <v>797</v>
+        <v>665</v>
       </c>
       <c r="C503" s="4" t="s">
         <v>528</v>
@@ -9836,7 +9833,7 @@
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A504" s="4" t="s">
-        <v>538</v>
+        <v>797</v>
       </c>
       <c r="C504" s="4" t="s">
         <v>810</v>
@@ -9848,7 +9845,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A505" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C505" s="4" t="s">
         <v>748</v>
@@ -9860,7 +9857,7 @@
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A506" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C506" s="4" t="s">
         <v>711</v>
@@ -9872,7 +9869,7 @@
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A507" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C507" s="4" t="s">
         <v>529</v>
@@ -9884,7 +9881,7 @@
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A508" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C508" s="4" t="s">
         <v>671</v>
@@ -9896,7 +9893,7 @@
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A509" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C509" s="4" t="s">
         <v>715</v>
@@ -9908,7 +9905,7 @@
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A510" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C510" s="4" t="s">
         <v>530</v>
@@ -9920,7 +9917,7 @@
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A511" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C511" s="4" t="s">
         <v>531</v>
@@ -9932,7 +9929,7 @@
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A512" s="4" t="s">
-        <v>259</v>
+        <v>545</v>
       </c>
       <c r="C512" s="4" t="s">
         <v>532</v>
@@ -9944,7 +9941,7 @@
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A513" s="4" t="s">
-        <v>765</v>
+        <v>259</v>
       </c>
       <c r="C513" s="4" t="s">
         <v>533</v>
@@ -9956,7 +9953,7 @@
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A514" s="4" t="s">
-        <v>957</v>
+        <v>765</v>
       </c>
       <c r="C514" s="4" t="s">
         <v>257</v>
@@ -9968,7 +9965,7 @@
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A515" s="4" t="s">
-        <v>546</v>
+        <v>957</v>
       </c>
       <c r="C515" s="4" t="s">
         <v>534</v>
@@ -9980,7 +9977,7 @@
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A516" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C516" s="4" t="s">
         <v>535</v>
@@ -9992,7 +9989,7 @@
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A517" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C517" s="4" t="s">
         <v>898</v>
@@ -10004,7 +10001,7 @@
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A518" s="4" t="s">
-        <v>710</v>
+        <v>548</v>
       </c>
       <c r="C518" s="4" t="s">
         <v>536</v>
@@ -10016,7 +10013,7 @@
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A519" s="4" t="s">
-        <v>549</v>
+        <v>710</v>
       </c>
       <c r="C519" s="4" t="s">
         <v>698</v>
@@ -10028,7 +10025,7 @@
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A520" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C520" s="4" t="s">
         <v>537</v>
@@ -10040,7 +10037,7 @@
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A521" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C521" s="29" t="s">
         <v>954</v>
@@ -10052,7 +10049,7 @@
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A522" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C522" s="4" t="s">
         <v>955</v>
@@ -10064,7 +10061,7 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A523" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C523" s="4" t="s">
         <v>863</v>
@@ -10076,7 +10073,7 @@
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A524" s="4" t="s">
-        <v>675</v>
+        <v>553</v>
       </c>
       <c r="C524" s="4" t="s">
         <v>258</v>
@@ -10088,7 +10085,7 @@
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A525" s="4" t="s">
-        <v>554</v>
+        <v>675</v>
       </c>
       <c r="C525" s="4" t="s">
         <v>665</v>
@@ -10100,7 +10097,7 @@
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A526" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C526" s="4" t="s">
         <v>797</v>
@@ -10112,7 +10109,7 @@
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A527" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C527" s="4" t="s">
         <v>538</v>
@@ -10124,7 +10121,7 @@
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A528" s="4" t="s">
-        <v>663</v>
+        <v>556</v>
       </c>
       <c r="C528" s="29" t="s">
         <v>956</v>
@@ -10136,7 +10133,7 @@
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A529" s="4" t="s">
-        <v>557</v>
+        <v>663</v>
       </c>
       <c r="C529" s="4" t="s">
         <v>539</v>
@@ -10148,7 +10145,7 @@
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A530" s="4" t="s">
-        <v>760</v>
+        <v>557</v>
       </c>
       <c r="C530" s="4" t="s">
         <v>540</v>
@@ -10160,7 +10157,7 @@
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A531" s="4" t="s">
-        <v>959</v>
+        <v>760</v>
       </c>
       <c r="C531" s="4" t="s">
         <v>541</v>
@@ -10172,7 +10169,7 @@
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A532" s="4" t="s">
-        <v>558</v>
+        <v>959</v>
       </c>
       <c r="C532" s="4" t="s">
         <v>542</v>
@@ -10184,7 +10181,7 @@
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A533" s="4" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C533" s="4" t="s">
         <v>543</v>
@@ -10196,7 +10193,7 @@
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A534" s="4" t="s">
-        <v>717</v>
+        <v>559</v>
       </c>
       <c r="C534" s="4" t="s">
         <v>544</v>
@@ -10208,7 +10205,7 @@
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A535" s="4" t="s">
-        <v>902</v>
+        <v>717</v>
       </c>
       <c r="C535" s="4" t="s">
         <v>545</v>
@@ -10220,7 +10217,7 @@
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A536" s="4" t="s">
-        <v>560</v>
+        <v>902</v>
       </c>
       <c r="C536" s="4" t="s">
         <v>259</v>
@@ -10232,7 +10229,7 @@
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A537" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C537" s="4" t="s">
         <v>765</v>
@@ -10244,7 +10241,7 @@
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A538" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C538" s="4" t="s">
         <v>957</v>
@@ -10256,7 +10253,7 @@
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A539" s="4" t="s">
-        <v>829</v>
+        <v>562</v>
       </c>
       <c r="C539" s="4" t="s">
         <v>546</v>
@@ -10268,7 +10265,7 @@
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A540" s="4" t="s">
-        <v>960</v>
+        <v>829</v>
       </c>
       <c r="C540" s="4" t="s">
         <v>547</v>
@@ -10280,7 +10277,7 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A541" s="4" t="s">
-        <v>563</v>
+        <v>960</v>
       </c>
       <c r="C541" s="4" t="s">
         <v>548</v>
@@ -10292,7 +10289,7 @@
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A542" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C542" s="4" t="s">
         <v>710</v>
@@ -10304,7 +10301,7 @@
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A543" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C543" s="4" t="s">
         <v>549</v>
@@ -10316,7 +10313,7 @@
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A544" s="4" t="s">
-        <v>750</v>
+        <v>565</v>
       </c>
       <c r="C544" s="4" t="s">
         <v>550</v>
@@ -10328,7 +10325,7 @@
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A545" s="4" t="s">
-        <v>566</v>
+        <v>750</v>
       </c>
       <c r="C545" s="29" t="s">
         <v>958</v>
@@ -10340,7 +10337,7 @@
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A546" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C546" s="4" t="s">
         <v>551</v>
@@ -10352,7 +10349,7 @@
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A547" s="4" t="s">
-        <v>901</v>
+        <v>567</v>
       </c>
       <c r="C547" s="4" t="s">
         <v>552</v>
@@ -10364,7 +10361,7 @@
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A548" s="4" t="s">
-        <v>568</v>
+        <v>901</v>
       </c>
       <c r="C548" s="4" t="s">
         <v>553</v>
@@ -10376,7 +10373,7 @@
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A549" s="4" t="s">
-        <v>742</v>
+        <v>568</v>
       </c>
       <c r="C549" s="4" t="s">
         <v>675</v>
@@ -10388,7 +10385,7 @@
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A550" s="4" t="s">
-        <v>569</v>
+        <v>742</v>
       </c>
       <c r="C550" s="4" t="s">
         <v>554</v>
@@ -10400,7 +10397,7 @@
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A551" s="4" t="s">
-        <v>740</v>
+        <v>569</v>
       </c>
       <c r="C551" s="4" t="s">
         <v>555</v>
@@ -10412,7 +10409,7 @@
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A552" s="4" t="s">
-        <v>570</v>
+        <v>740</v>
       </c>
       <c r="C552" s="4" t="s">
         <v>556</v>
@@ -10424,7 +10421,7 @@
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A553" s="4" t="s">
-        <v>761</v>
+        <v>570</v>
       </c>
       <c r="C553" s="4" t="s">
         <v>663</v>
@@ -10436,7 +10433,7 @@
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A554" s="4" t="s">
-        <v>571</v>
+        <v>761</v>
       </c>
       <c r="C554" s="4" t="s">
         <v>557</v>
@@ -10448,7 +10445,7 @@
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A555" s="4" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C555" s="4" t="s">
         <v>760</v>
@@ -10460,7 +10457,7 @@
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A556" s="4" t="s">
-        <v>755</v>
+        <v>572</v>
       </c>
       <c r="C556" s="4" t="s">
         <v>959</v>
@@ -10472,7 +10469,7 @@
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A557" s="4" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
       <c r="C557" s="4" t="s">
         <v>558</v>
@@ -10484,7 +10481,7 @@
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A558" s="4" t="s">
-        <v>790</v>
+        <v>764</v>
       </c>
       <c r="C558" s="4" t="s">
         <v>559</v>
@@ -10496,7 +10493,7 @@
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A559" s="4" t="s">
-        <v>689</v>
+        <v>790</v>
       </c>
       <c r="C559" s="4" t="s">
         <v>717</v>
@@ -10508,7 +10505,7 @@
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A560" s="4" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="C560" s="4" t="s">
         <v>902</v>
@@ -10520,7 +10517,7 @@
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A561" s="4" t="s">
-        <v>573</v>
+        <v>696</v>
       </c>
       <c r="C561" s="4" t="s">
         <v>560</v>
@@ -10532,7 +10529,7 @@
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A562" s="4" t="s">
-        <v>963</v>
+        <v>573</v>
       </c>
       <c r="C562" s="4" t="s">
         <v>561</v>
@@ -10544,7 +10541,7 @@
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A563" s="4" t="s">
-        <v>685</v>
+        <v>963</v>
       </c>
       <c r="C563" s="4" t="s">
         <v>562</v>
@@ -10556,7 +10553,7 @@
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A564" s="4" t="s">
-        <v>574</v>
+        <v>685</v>
       </c>
       <c r="C564" s="4" t="s">
         <v>829</v>
@@ -10568,7 +10565,7 @@
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A565" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C565" s="4" t="s">
         <v>960</v>
@@ -10580,7 +10577,7 @@
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A566" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C566" s="4" t="s">
         <v>563</v>
@@ -10592,7 +10589,7 @@
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A567" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C567" s="4" t="s">
         <v>564</v>
@@ -10604,7 +10601,7 @@
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A568" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C568" s="4" t="s">
         <v>565</v>
@@ -10616,7 +10613,7 @@
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A569" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C569" s="4" t="s">
         <v>750</v>
@@ -10628,7 +10625,7 @@
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A570" s="4" t="s">
-        <v>735</v>
+        <v>579</v>
       </c>
       <c r="C570" s="29" t="s">
         <v>961</v>
@@ -10640,7 +10637,7 @@
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A571" s="4" t="s">
-        <v>580</v>
+        <v>735</v>
       </c>
       <c r="C571" s="4" t="s">
         <v>566</v>
@@ -10652,7 +10649,7 @@
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A572" s="4" t="s">
-        <v>815</v>
+        <v>580</v>
       </c>
       <c r="C572" s="4" t="s">
         <v>567</v>
@@ -10664,7 +10661,7 @@
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A573" s="4" t="s">
-        <v>581</v>
+        <v>815</v>
       </c>
       <c r="C573" s="4" t="s">
         <v>901</v>
@@ -10676,7 +10673,7 @@
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A574" s="4" t="s">
-        <v>868</v>
+        <v>581</v>
       </c>
       <c r="C574" s="4" t="s">
         <v>568</v>
@@ -10688,7 +10685,7 @@
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A575" s="4" t="s">
-        <v>831</v>
+        <v>868</v>
       </c>
       <c r="C575" s="4" t="s">
         <v>742</v>
@@ -10700,7 +10697,7 @@
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A576" s="4" t="s">
-        <v>582</v>
+        <v>831</v>
       </c>
       <c r="C576" s="4" t="s">
         <v>569</v>
@@ -10712,7 +10709,7 @@
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A577" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C577" s="4" t="s">
         <v>740</v>
@@ -10724,7 +10721,7 @@
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A578" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C578" s="4" t="s">
         <v>570</v>
@@ -10736,7 +10733,7 @@
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A579" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C579" s="4" t="s">
         <v>761</v>
@@ -10748,7 +10745,7 @@
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A580" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C580" s="4" t="s">
         <v>571</v>
@@ -10760,7 +10757,7 @@
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A581" s="4" t="s">
-        <v>871</v>
+        <v>586</v>
       </c>
       <c r="C581" s="4" t="s">
         <v>572</v>
@@ -10772,7 +10769,7 @@
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A582" s="4" t="s">
-        <v>587</v>
+        <v>871</v>
       </c>
       <c r="C582" s="4" t="s">
         <v>755</v>
@@ -10784,7 +10781,7 @@
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A583" s="4" t="s">
-        <v>966</v>
+        <v>587</v>
       </c>
       <c r="C583" s="4" t="s">
         <v>764</v>
@@ -10796,7 +10793,7 @@
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A584" s="4" t="s">
-        <v>835</v>
+        <v>966</v>
       </c>
       <c r="C584" s="4" t="s">
         <v>790</v>
@@ -10808,7 +10805,7 @@
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A585" s="4" t="s">
-        <v>588</v>
+        <v>835</v>
       </c>
       <c r="C585" s="4" t="s">
         <v>689</v>
@@ -10820,7 +10817,7 @@
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A586" s="4" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C586" s="4" t="s">
         <v>696</v>
@@ -10832,7 +10829,7 @@
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A587" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C587" s="29" t="s">
         <v>962</v>
@@ -10844,7 +10841,7 @@
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A588" s="4" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C588" s="4" t="s">
         <v>573</v>
@@ -10856,7 +10853,7 @@
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A589" s="4" t="s">
-        <v>693</v>
+        <v>591</v>
       </c>
       <c r="C589" s="4" t="s">
         <v>963</v>
@@ -10868,7 +10865,7 @@
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A590" s="4" t="s">
-        <v>592</v>
+        <v>693</v>
       </c>
       <c r="C590" s="4" t="s">
         <v>685</v>
@@ -10880,7 +10877,7 @@
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A591" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C591" s="4" t="s">
         <v>574</v>
@@ -10892,7 +10889,7 @@
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A592" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C592" s="4" t="s">
         <v>575</v>
@@ -10904,7 +10901,7 @@
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A593" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C593" s="29" t="s">
         <v>964</v>
@@ -10916,7 +10913,7 @@
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A594" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C594" s="4" t="s">
         <v>576</v>
@@ -10928,7 +10925,7 @@
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A595" s="4" t="s">
-        <v>968</v>
+        <v>596</v>
       </c>
       <c r="C595" s="4" t="s">
         <v>577</v>
@@ -10940,7 +10937,7 @@
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A596" s="4" t="s">
-        <v>597</v>
+        <v>968</v>
       </c>
       <c r="C596" s="4" t="s">
         <v>578</v>
@@ -10952,7 +10949,7 @@
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A597" s="4" t="s">
-        <v>869</v>
+        <v>597</v>
       </c>
       <c r="C597" s="4" t="s">
         <v>579</v>
@@ -10964,7 +10961,7 @@
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A598" s="4" t="s">
-        <v>598</v>
+        <v>869</v>
       </c>
       <c r="C598" s="4" t="s">
         <v>735</v>
@@ -10976,7 +10973,7 @@
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A599" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C599" s="4" t="s">
         <v>580</v>
@@ -10988,7 +10985,7 @@
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A600" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C600" s="4" t="s">
         <v>815</v>
@@ -11000,7 +10997,7 @@
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A601" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C601" s="4" t="s">
         <v>581</v>
@@ -11012,7 +11009,7 @@
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A602" s="4" t="s">
-        <v>969</v>
+        <v>601</v>
       </c>
       <c r="C602" s="29" t="s">
         <v>965</v>
@@ -11024,7 +11021,7 @@
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A603" s="4" t="s">
-        <v>862</v>
+        <v>969</v>
       </c>
       <c r="C603" s="4" t="s">
         <v>868</v>
@@ -11036,7 +11033,7 @@
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A604" s="4" t="s">
-        <v>794</v>
+        <v>862</v>
       </c>
       <c r="C604" s="4" t="s">
         <v>831</v>
@@ -11048,7 +11045,7 @@
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A605" s="4" t="s">
-        <v>705</v>
+        <v>794</v>
       </c>
       <c r="C605" s="4" t="s">
         <v>582</v>
@@ -11060,7 +11057,7 @@
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A606" s="4" t="s">
-        <v>602</v>
+        <v>705</v>
       </c>
       <c r="C606" s="4" t="s">
         <v>583</v>
@@ -11072,7 +11069,7 @@
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A607" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C607" s="4" t="s">
         <v>584</v>
@@ -11084,7 +11081,7 @@
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A608" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C608" s="4" t="s">
         <v>585</v>
@@ -11096,7 +11093,7 @@
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A609" s="4" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C609" s="4" t="s">
         <v>586</v>
@@ -11108,7 +11105,7 @@
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A610" s="4" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C610" s="4" t="s">
         <v>871</v>
@@ -11120,7 +11117,7 @@
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A611" s="4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C611" s="4" t="s">
         <v>587</v>
@@ -11132,7 +11129,7 @@
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A612" s="4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C612" s="4" t="s">
         <v>966</v>
@@ -11144,7 +11141,7 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A613" s="4" t="s">
-        <v>768</v>
+        <v>608</v>
       </c>
       <c r="C613" s="4" t="s">
         <v>835</v>
@@ -11156,7 +11153,7 @@
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A614" s="4" t="s">
-        <v>609</v>
+        <v>768</v>
       </c>
       <c r="C614" s="4" t="s">
         <v>588</v>
@@ -11168,7 +11165,7 @@
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A615" s="4" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C615" s="4" t="s">
         <v>589</v>
@@ -11180,7 +11177,7 @@
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A616" s="4" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C616" s="4" t="s">
         <v>590</v>
@@ -11192,7 +11189,7 @@
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A617" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C617" s="4" t="s">
         <v>591</v>
@@ -11204,7 +11201,7 @@
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A618" s="4" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C618" s="4" t="s">
         <v>693</v>
@@ -11216,7 +11213,7 @@
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A619" s="4" t="s">
-        <v>798</v>
+        <v>613</v>
       </c>
       <c r="C619" s="4" t="s">
         <v>592</v>
@@ -11228,7 +11225,7 @@
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A620" s="4" t="s">
-        <v>775</v>
+        <v>798</v>
       </c>
       <c r="C620" s="4" t="s">
         <v>593</v>
@@ -11240,7 +11237,7 @@
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A621" s="4" t="s">
-        <v>614</v>
+        <v>775</v>
       </c>
       <c r="C621" s="4" t="s">
         <v>594</v>
@@ -11252,7 +11249,7 @@
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A622" s="4" t="s">
-        <v>836</v>
+        <v>614</v>
       </c>
       <c r="C622" s="29" t="s">
         <v>967</v>
@@ -11264,7 +11261,7 @@
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A623" s="4" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="C623" s="4" t="s">
         <v>595</v>
@@ -11276,7 +11273,7 @@
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A624" s="4" t="s">
-        <v>830</v>
+        <v>842</v>
       </c>
       <c r="C624" s="4" t="s">
         <v>596</v>
@@ -11288,7 +11285,7 @@
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A625" s="4" t="s">
-        <v>615</v>
+        <v>830</v>
       </c>
       <c r="C625" s="4" t="s">
         <v>968</v>
@@ -11300,7 +11297,7 @@
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A626" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C626" s="4" t="s">
         <v>597</v>
@@ -11312,7 +11309,7 @@
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A627" s="4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C627" s="4" t="s">
         <v>869</v>
@@ -11324,7 +11321,7 @@
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A628" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C628" s="4" t="s">
         <v>598</v>
@@ -11336,7 +11333,7 @@
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A629" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C629" s="4" t="s">
         <v>599</v>
@@ -11348,7 +11345,7 @@
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A630" s="4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C630" s="4" t="s">
         <v>600</v>
@@ -11360,7 +11357,7 @@
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A631" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C631" s="4" t="s">
         <v>601</v>
@@ -11372,7 +11369,7 @@
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A632" s="4" t="s">
-        <v>885</v>
+        <v>621</v>
       </c>
       <c r="C632" s="4" t="s">
         <v>969</v>
@@ -11384,7 +11381,7 @@
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A633" s="4" t="s">
-        <v>622</v>
+        <v>885</v>
       </c>
       <c r="C633" s="4" t="s">
         <v>862</v>
@@ -11396,7 +11393,7 @@
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A634" s="4" t="s">
-        <v>260</v>
+        <v>622</v>
       </c>
       <c r="C634" s="29" t="s">
         <v>970</v>
@@ -11408,7 +11405,7 @@
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A635" s="4" t="s">
-        <v>691</v>
+        <v>260</v>
       </c>
       <c r="C635" s="4" t="s">
         <v>794</v>
@@ -11420,7 +11417,7 @@
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A636" s="4" t="s">
-        <v>668</v>
+        <v>691</v>
       </c>
       <c r="C636" s="4" t="s">
         <v>705</v>
@@ -11432,7 +11429,7 @@
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A637" s="4" t="s">
-        <v>623</v>
+        <v>668</v>
       </c>
       <c r="C637" s="4" t="s">
         <v>602</v>
@@ -11444,7 +11441,7 @@
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A638" s="4" t="s">
-        <v>680</v>
+        <v>623</v>
       </c>
       <c r="C638" s="4" t="s">
         <v>603</v>
@@ -11456,7 +11453,7 @@
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A639" s="4" t="s">
-        <v>770</v>
+        <v>680</v>
       </c>
       <c r="C639" s="4" t="s">
         <v>604</v>
@@ -11468,7 +11465,7 @@
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A640" s="4" t="s">
-        <v>624</v>
+        <v>770</v>
       </c>
       <c r="C640" s="4" t="s">
         <v>605</v>
@@ -11480,7 +11477,7 @@
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A641" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C641" s="4" t="s">
         <v>606</v>
@@ -11492,7 +11489,7 @@
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A642" s="4" t="s">
-        <v>859</v>
+        <v>625</v>
       </c>
       <c r="C642" s="4" t="s">
         <v>607</v>
@@ -11504,7 +11501,7 @@
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A643" s="4" t="s">
-        <v>872</v>
+        <v>859</v>
       </c>
       <c r="C643" s="4" t="s">
         <v>608</v>
@@ -11516,7 +11513,7 @@
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A644" s="4" t="s">
-        <v>754</v>
+        <v>872</v>
       </c>
       <c r="C644" s="29" t="s">
         <v>971</v>
@@ -11528,7 +11525,7 @@
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A645" s="4" t="s">
-        <v>626</v>
+        <v>754</v>
       </c>
       <c r="C645" s="4" t="s">
         <v>768</v>
@@ -11540,7 +11537,7 @@
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A646" s="4" t="s">
-        <v>800</v>
+        <v>626</v>
       </c>
       <c r="C646" s="4" t="s">
         <v>609</v>
@@ -11552,7 +11549,7 @@
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A647" s="4" t="s">
-        <v>973</v>
+        <v>800</v>
       </c>
       <c r="C647" s="4" t="s">
         <v>610</v>
@@ -11564,7 +11561,7 @@
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A648" s="4" t="s">
-        <v>627</v>
+        <v>973</v>
       </c>
       <c r="C648" s="4" t="s">
         <v>611</v>
@@ -11576,7 +11573,7 @@
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A649" s="4" t="s">
-        <v>716</v>
+        <v>627</v>
       </c>
       <c r="C649" s="4" t="s">
         <v>612</v>
@@ -11588,7 +11585,7 @@
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A650" s="4" t="s">
-        <v>672</v>
+        <v>716</v>
       </c>
       <c r="C650" s="4" t="s">
         <v>613</v>
@@ -11600,7 +11597,7 @@
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A651" s="4" t="s">
-        <v>628</v>
+        <v>672</v>
       </c>
       <c r="C651" s="4" t="s">
         <v>798</v>
@@ -11612,7 +11609,7 @@
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A652" s="4" t="s">
-        <v>261</v>
+        <v>628</v>
       </c>
       <c r="C652" s="4" t="s">
         <v>775</v>
@@ -11624,7 +11621,7 @@
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A653" s="4" t="s">
-        <v>629</v>
+        <v>261</v>
       </c>
       <c r="C653" s="4" t="s">
         <v>614</v>
@@ -11636,7 +11633,7 @@
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A654" s="4" t="s">
-        <v>743</v>
+        <v>629</v>
       </c>
       <c r="C654" s="4" t="s">
         <v>836</v>
@@ -11648,7 +11645,7 @@
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A655" s="4" t="s">
-        <v>630</v>
+        <v>743</v>
       </c>
       <c r="C655" s="4" t="s">
         <v>842</v>
@@ -11660,7 +11657,7 @@
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A656" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C656" s="4" t="s">
         <v>830</v>
@@ -11672,7 +11669,7 @@
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A657" s="4" t="s">
-        <v>777</v>
+        <v>631</v>
       </c>
       <c r="C657" s="4" t="s">
         <v>615</v>
@@ -11684,7 +11681,7 @@
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A658" s="4" t="s">
-        <v>877</v>
+        <v>777</v>
       </c>
       <c r="C658" s="4" t="s">
         <v>616</v>
@@ -11696,7 +11693,7 @@
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A659" s="4" t="s">
-        <v>632</v>
+        <v>877</v>
       </c>
       <c r="C659" s="4" t="s">
         <v>617</v>
@@ -11708,7 +11705,7 @@
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A660" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C660" s="29" t="s">
         <v>972</v>
@@ -11720,7 +11717,7 @@
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A661" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C661" s="4" t="s">
         <v>618</v>
@@ -11732,7 +11729,7 @@
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A662" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C662" s="4" t="s">
         <v>619</v>
@@ -11744,7 +11741,7 @@
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A663" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C663" s="4" t="s">
         <v>620</v>
@@ -11756,7 +11753,7 @@
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A664" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C664" s="4" t="s">
         <v>621</v>
@@ -11768,7 +11765,7 @@
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A665" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C665" s="4" t="s">
         <v>885</v>
@@ -11780,7 +11777,7 @@
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A666" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C666" s="4" t="s">
         <v>622</v>
@@ -11792,7 +11789,7 @@
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A667" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C667" s="4" t="s">
         <v>260</v>
@@ -11804,7 +11801,7 @@
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A668" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C668" s="4" t="s">
         <v>691</v>
@@ -11816,7 +11813,7 @@
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A669" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C669" s="4" t="s">
         <v>668</v>
@@ -11828,7 +11825,7 @@
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A670" s="4" t="s">
-        <v>974</v>
+        <v>642</v>
       </c>
       <c r="C670" s="4" t="s">
         <v>623</v>
@@ -11840,7 +11837,7 @@
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A671" s="4" t="s">
-        <v>643</v>
+        <v>974</v>
       </c>
       <c r="C671" s="4" t="s">
         <v>680</v>
@@ -11852,7 +11849,7 @@
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A672" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C672" s="4" t="s">
         <v>770</v>
@@ -11864,7 +11861,7 @@
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A673" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C673" s="4" t="s">
         <v>624</v>
@@ -11876,7 +11873,7 @@
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A674" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C674" s="4" t="s">
         <v>625</v>
@@ -11888,7 +11885,7 @@
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A675" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C675" s="4" t="s">
         <v>859</v>
@@ -11900,7 +11897,7 @@
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A676" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C676" s="4" t="s">
         <v>872</v>
@@ -11912,7 +11909,7 @@
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A677" s="4" t="s">
-        <v>886</v>
+        <v>648</v>
       </c>
       <c r="C677" s="4" t="s">
         <v>754</v>
@@ -11924,7 +11921,7 @@
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A678" s="4" t="s">
-        <v>976</v>
+        <v>886</v>
       </c>
       <c r="C678" s="4" t="s">
         <v>626</v>
@@ -11936,7 +11933,7 @@
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A679" s="4" t="s">
-        <v>649</v>
+        <v>976</v>
       </c>
       <c r="C679" s="4" t="s">
         <v>800</v>
@@ -11948,7 +11945,7 @@
     </row>
     <row r="680" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A680" s="4" t="s">
-        <v>782</v>
+        <v>649</v>
       </c>
       <c r="C680" s="4" t="s">
         <v>973</v>
@@ -11960,7 +11957,7 @@
     </row>
     <row r="681" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A681" s="4" t="s">
-        <v>838</v>
+        <v>782</v>
       </c>
       <c r="C681" s="4" t="s">
         <v>627</v>
@@ -11972,7 +11969,7 @@
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A682" s="4" t="s">
-        <v>756</v>
+        <v>838</v>
       </c>
       <c r="C682" s="4" t="s">
         <v>716</v>
@@ -11984,7 +11981,7 @@
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A683" s="4" t="s">
-        <v>650</v>
+        <v>756</v>
       </c>
       <c r="C683" s="4" t="s">
         <v>672</v>
@@ -11996,7 +11993,7 @@
     </row>
     <row r="684" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A684" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C684" s="4" t="s">
         <v>628</v>
@@ -12008,7 +12005,7 @@
     </row>
     <row r="685" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A685" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C685" s="4" t="s">
         <v>261</v>
@@ -12020,7 +12017,7 @@
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A686" s="4" t="s">
-        <v>776</v>
+        <v>652</v>
       </c>
       <c r="C686" s="4" t="s">
         <v>629</v>
@@ -12032,7 +12029,7 @@
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A687" s="4" t="s">
-        <v>653</v>
+        <v>776</v>
       </c>
       <c r="C687" s="4" t="s">
         <v>743</v>
@@ -12044,7 +12041,7 @@
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A688" s="4" t="s">
-        <v>264</v>
+        <v>653</v>
       </c>
       <c r="C688" s="4" t="s">
         <v>630</v>
@@ -12056,7 +12053,7 @@
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A689" s="4" t="s">
-        <v>654</v>
+        <v>264</v>
       </c>
       <c r="C689" s="4" t="s">
         <v>631</v>
@@ -12068,7 +12065,7 @@
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A690" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C690" s="4" t="s">
         <v>777</v>
@@ -12080,7 +12077,7 @@
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A691" s="4" t="s">
-        <v>729</v>
+        <v>655</v>
       </c>
       <c r="C691" s="4" t="s">
         <v>877</v>
@@ -12092,7 +12089,7 @@
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A692" s="4" t="s">
-        <v>977</v>
+        <v>729</v>
       </c>
       <c r="C692" s="4" t="s">
         <v>632</v>
@@ -12104,7 +12101,7 @@
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A693" s="4" t="s">
-        <v>686</v>
+        <v>977</v>
       </c>
       <c r="C693" s="4" t="s">
         <v>633</v>
@@ -12116,7 +12113,7 @@
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A694" s="4" t="s">
-        <v>882</v>
+        <v>686</v>
       </c>
       <c r="C694" s="4" t="s">
         <v>634</v>
@@ -12128,7 +12125,7 @@
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A695" s="4" t="s">
-        <v>793</v>
+        <v>882</v>
       </c>
       <c r="C695" s="4" t="s">
         <v>635</v>
@@ -12140,7 +12137,7 @@
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A696" s="4" t="s">
-        <v>656</v>
+        <v>793</v>
       </c>
       <c r="C696" s="4" t="s">
         <v>636</v>
@@ -12152,7 +12149,7 @@
     </row>
     <row r="697" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A697" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C697" s="4" t="s">
         <v>637</v>
@@ -12164,7 +12161,7 @@
     </row>
     <row r="698" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A698" s="4" t="s">
-        <v>681</v>
+        <v>657</v>
       </c>
       <c r="C698" s="4" t="s">
         <v>638</v>
@@ -12176,7 +12173,7 @@
     </row>
     <row r="699" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A699" s="4" t="s">
-        <v>658</v>
+        <v>681</v>
       </c>
       <c r="C699" s="4" t="s">
         <v>639</v>
@@ -12188,7 +12185,7 @@
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A700" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C700" s="4" t="s">
         <v>640</v>
@@ -12200,7 +12197,7 @@
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A701" s="4" t="s">
-        <v>706</v>
+        <v>659</v>
       </c>
       <c r="C701" s="4" t="s">
         <v>641</v>
@@ -12212,7 +12209,7 @@
     </row>
     <row r="702" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A702" s="4" t="s">
-        <v>660</v>
+        <v>706</v>
       </c>
       <c r="C702" s="4" t="s">
         <v>642</v>
@@ -12223,6 +12220,9 @@
       </c>
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A703" s="4" t="s">
+        <v>660</v>
+      </c>
       <c r="C703" s="4" t="s">
         <v>974</v>
       </c>
@@ -12263,7 +12263,7 @@
         <v>646</v>
       </c>
       <c r="D707" s="4" t="str">
-        <f t="shared" ref="D707:D770" si="11">VLOOKUP(C707,A:A,1,0)</f>
+        <f t="shared" ref="D707:D736" si="11">VLOOKUP(C707,A:A,1,0)</f>
         <v>WELL</v>
       </c>
     </row>
